--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.29598992809341</v>
+        <v>7.685598363315179</v>
       </c>
       <c r="D2" t="n">
-        <v>47.66436348951468</v>
+        <v>7.745459067046135</v>
       </c>
       <c r="E2" t="n">
-        <v>10.54883137406701</v>
+        <v>1.714185098285888</v>
       </c>
       <c r="F2" t="n">
-        <v>11.52684134981378</v>
+        <v>1.87311171934474</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.11323871965219</v>
+        <v>5.868401291943482</v>
       </c>
       <c r="D3" t="n">
-        <v>36.4876516456513</v>
+        <v>5.929243392418337</v>
       </c>
       <c r="E3" t="n">
-        <v>10.54883137406701</v>
+        <v>1.714185098285888</v>
       </c>
       <c r="F3" t="n">
-        <v>11.52684134981378</v>
+        <v>1.87311171934474</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.49414670888081</v>
+        <v>3.492798840193131</v>
       </c>
       <c r="D4" t="n">
-        <v>20.63955239336201</v>
+        <v>3.353927263921327</v>
       </c>
       <c r="E4" t="n">
-        <v>10.54883137406701</v>
+        <v>1.714185098285888</v>
       </c>
       <c r="F4" t="n">
-        <v>11.52684134981378</v>
+        <v>1.87311171934474</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.59096258203753</v>
+        <v>3.346031419581099</v>
       </c>
       <c r="D5" t="n">
-        <v>16.89507924012355</v>
+        <v>2.745450376520078</v>
       </c>
       <c r="E5" t="n">
-        <v>10.54883137406701</v>
+        <v>1.714185098285888</v>
       </c>
       <c r="F5" t="n">
-        <v>11.52684134981378</v>
+        <v>1.87311171934474</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.25398515412121</v>
+        <v>3.616272587544697</v>
       </c>
       <c r="D6" t="n">
-        <v>22.3923977964843</v>
+        <v>3.638764641928698</v>
       </c>
       <c r="E6" t="n">
-        <v>10.54883137406701</v>
+        <v>1.714185098285888</v>
       </c>
       <c r="F6" t="n">
-        <v>11.52684134981378</v>
+        <v>1.87311171934474</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
